--- a/DDM GD Find Alpha Rebuild/deme_51_alpha_results_summary.xlsx
+++ b/DDM GD Find Alpha Rebuild/deme_51_alpha_results_summary.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C59FF0-81B0-4D3D-9814-798273A5B172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05607A76-FA70-4279-9954-AEB28EA3CF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -413,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
@@ -421,7 +432,7 @@
     <col min="14" max="14" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +488,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>51</v>
       </c>
@@ -533,7 +544,7 @@
         <v>8.1479215621948242</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>51</v>
       </c>
@@ -589,7 +600,7 @@
         <v>8.1549434661865234</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>51</v>
       </c>
@@ -645,7 +656,7 @@
         <v>8.1407690048217773</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>51</v>
       </c>
@@ -701,7 +712,7 @@
         <v>8.1533346176147461</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>51</v>
       </c>
@@ -757,7 +768,7 @@
         <v>8.1572513580322266</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>51</v>
       </c>
@@ -813,7 +824,7 @@
         <v>8.1495180130004883</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>51</v>
       </c>
@@ -869,7 +880,7 @@
         <v>8.1508693695068359</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>51</v>
       </c>
@@ -925,7 +936,7 @@
         <v>8.1462173461914063</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>51</v>
       </c>
@@ -981,7 +992,7 @@
         <v>8.1587648391723633</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>51</v>
       </c>
@@ -1036,8 +1047,12 @@
       <c r="R11">
         <v>8.1568746566772461</v>
       </c>
+      <c r="S11">
+        <f>(N11/B11)*100</f>
+        <v>1.4692435235329225E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>51</v>
       </c>
@@ -1091,6 +1106,10 @@
       </c>
       <c r="R12">
         <v>8.1485652923583984</v>
+      </c>
+      <c r="S12">
+        <f>(N12/B12)*100</f>
+        <v>2.1383367433142782E-2</v>
       </c>
     </row>
   </sheetData>
